--- a/student_assignment_03/outputs/excel/excel_to_word.xlsx
+++ b/student_assignment_03/outputs/excel/excel_to_word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\truenas-kresimir-share-cp\FSB\semestar_09\interakcija-covjeka-i-robota\interakcija-covjeka-i-robota\student_assignment_03\outputs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BBD4A1-4DE4-4D96-9E6C-F5CBED085770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B70C03-32FD-417A-BDD2-2101E81EB661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7C6AB4B3-0BDA-4F60-8756-2F5BEB28C5D1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>ID Slike</t>
   </si>
@@ -105,6 +105,36 @@
   </si>
   <si>
     <t>Razlika</t>
+  </si>
+  <si>
+    <t>body_pose_estimation_02</t>
+  </si>
+  <si>
+    <r>
+      <t>Lakat (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>°</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Koljeno (°)</t>
   </si>
 </sst>
 </file>
@@ -482,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A9F1B7-95EF-4908-A524-EC826786FE6E}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -752,6 +782,137 @@
         <v>44.6</v>
       </c>
     </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>47.39</v>
+      </c>
+      <c r="C11">
+        <v>171.14</v>
+      </c>
+      <c r="K11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>46.42</v>
+      </c>
+      <c r="C12">
+        <v>172.75</v>
+      </c>
+      <c r="K12" t="str">
+        <f>LEFT(A11, LEN(A11)-4)</f>
+        <v>000001</v>
+      </c>
+      <c r="L12">
+        <f>B11</f>
+        <v>47.39</v>
+      </c>
+      <c r="M12">
+        <f>C11</f>
+        <v>171.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>41.47</v>
+      </c>
+      <c r="C13">
+        <v>179.18</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" ref="K13:K16" si="4">LEFT(A12, LEN(A12)-4)</f>
+        <v>000005</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ref="L13:L16" si="5">B12</f>
+        <v>46.42</v>
+      </c>
+      <c r="M13">
+        <f t="shared" ref="M13:M16" si="6">C12</f>
+        <v>172.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>34.21</v>
+      </c>
+      <c r="C14">
+        <v>175.42</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="4"/>
+        <v>000010</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="5"/>
+        <v>41.47</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="6"/>
+        <v>179.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>38.54</v>
+      </c>
+      <c r="C15">
+        <v>176.23</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="4"/>
+        <v>000015</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="5"/>
+        <v>34.21</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="6"/>
+        <v>175.42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K16" t="str">
+        <f t="shared" si="4"/>
+        <v>000020</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="5"/>
+        <v>38.54</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="6"/>
+        <v>176.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/student_assignment_03/outputs/excel/excel_to_word.xlsx
+++ b/student_assignment_03/outputs/excel/excel_to_word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\truenas-kresimir-share-cp\FSB\semestar_09\interakcija-covjeka-i-robota\interakcija-covjeka-i-robota\student_assignment_03\outputs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B70C03-32FD-417A-BDD2-2101E81EB661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C45289-E194-4365-8139-99CCAB311232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7C6AB4B3-0BDA-4F60-8756-2F5BEB28C5D1}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +154,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -176,8 +182,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A9F1B7-95EF-4908-A524-EC826786FE6E}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -577,10 +586,10 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="C4">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="D4">
         <v>216</v>
@@ -589,13 +598,13 @@
         <v>76</v>
       </c>
       <c r="F4">
-        <v>-27</v>
+        <v>-1</v>
       </c>
       <c r="G4">
-        <v>-46</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>53.34</v>
+        <v>5</v>
       </c>
       <c r="K4" t="str">
         <f>LEFT(A4, LEN(A4)-4)</f>
@@ -603,7 +612,7 @@
       </c>
       <c r="L4" t="str">
         <f>B4&amp;", "&amp;C4</f>
-        <v>243, 122</v>
+        <v>217, 75</v>
       </c>
       <c r="M4" t="str">
         <f>D4&amp;", "&amp;E4</f>
@@ -611,7 +620,7 @@
       </c>
       <c r="N4">
         <f>H4</f>
-        <v>53.34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -619,10 +628,10 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="C5">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="D5">
         <v>217</v>
@@ -631,13 +640,13 @@
         <v>64</v>
       </c>
       <c r="F5">
-        <v>-29</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>-55</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>62.18</v>
+        <v>5</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" ref="K5:K8" si="0">LEFT(A5, LEN(A5)-4)</f>
@@ -645,7 +654,7 @@
       </c>
       <c r="L5" t="str">
         <f t="shared" ref="L5:L8" si="1">B5&amp;", "&amp;C5</f>
-        <v>246, 119</v>
+        <v>216, 63</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" ref="M5:M8" si="2">D5&amp;", "&amp;E5</f>
@@ -653,7 +662,7 @@
       </c>
       <c r="N5">
         <f t="shared" ref="N5:N8" si="3">H5</f>
-        <v>62.18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -661,10 +670,10 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="C6">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>219</v>
@@ -673,13 +682,13 @@
         <v>48</v>
       </c>
       <c r="F6">
-        <v>-27</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>-67</v>
+        <v>-6</v>
       </c>
       <c r="H6">
-        <v>72.239999999999995</v>
+        <v>5</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="0"/>
@@ -687,7 +696,7 @@
       </c>
       <c r="L6" t="str">
         <f t="shared" si="1"/>
-        <v>246, 115</v>
+        <v>214, 54</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" si="2"/>
@@ -695,7 +704,7 @@
       </c>
       <c r="N6">
         <f t="shared" si="3"/>
-        <v>72.239999999999995</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -703,10 +712,10 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="C7">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>214</v>
@@ -715,13 +724,13 @@
         <v>76</v>
       </c>
       <c r="F7">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>-35</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>47.42</v>
+        <v>5</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
@@ -729,7 +738,7 @@
       </c>
       <c r="L7" t="str">
         <f t="shared" si="1"/>
-        <v>246, 111</v>
+        <v>214, 63</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="2"/>
@@ -737,7 +746,7 @@
       </c>
       <c r="N7">
         <f t="shared" si="3"/>
-        <v>47.42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -745,10 +754,10 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="C8">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>215</v>
@@ -757,13 +766,13 @@
         <v>72</v>
       </c>
       <c r="F8">
-        <v>-30</v>
+        <v>-1</v>
       </c>
       <c r="G8">
-        <v>-33</v>
+        <v>-7</v>
       </c>
       <c r="H8">
-        <v>44.6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
@@ -771,7 +780,7 @@
       </c>
       <c r="L8" t="str">
         <f t="shared" si="1"/>
-        <v>245, 105</v>
+        <v>216, 79</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="2"/>
@@ -779,7 +788,7 @@
       </c>
       <c r="N8">
         <f t="shared" si="3"/>
-        <v>44.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -913,6 +922,21 @@
         <v>176.23</v>
       </c>
     </row>
+    <row r="30" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P34" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/student_assignment_03/outputs/excel/excel_to_word.xlsx
+++ b/student_assignment_03/outputs/excel/excel_to_word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\truenas-kresimir-share-cp\FSB\semestar_09\interakcija-covjeka-i-robota\interakcija-covjeka-i-robota\student_assignment_03\outputs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C45289-E194-4365-8139-99CCAB311232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE34A7F-56A7-4DE4-B30E-8D1E0470A5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7C6AB4B3-0BDA-4F60-8756-2F5BEB28C5D1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
   <si>
     <t>ID Slike</t>
   </si>
@@ -135,6 +135,141 @@
   </si>
   <si>
     <t>Koljeno (°)</t>
+  </si>
+  <si>
+    <r>
+      <t>Nagib (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>°</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>head_pose_estimation_01</t>
+  </si>
+  <si>
+    <t>Frame</t>
+  </si>
+  <si>
+    <t>Opis</t>
+  </si>
+  <si>
+    <t>Osoba gleda ravno, u desno, s nagibom u desno</t>
+  </si>
+  <si>
+    <t>Osoba gleda ravno, u lijevo, bez nagiba</t>
+  </si>
+  <si>
+    <t>Pitch (°)</t>
+  </si>
+  <si>
+    <t>Yaw (°)</t>
+  </si>
+  <si>
+    <t>Roll (°)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osoba gleda ravno, blago u desno, bez nagiba, </t>
+  </si>
+  <si>
+    <t>Pitch (Â°)</t>
+  </si>
+  <si>
+    <t>Yaw (Â°)</t>
+  </si>
+  <si>
+    <t>Roll (Â°)</t>
+  </si>
+  <si>
+    <t>Pitch Klasifikacija</t>
+  </si>
+  <si>
+    <t>Yaw Klasifikacija</t>
+  </si>
+  <si>
+    <t>Roll Klasifikacija</t>
+  </si>
+  <si>
+    <t>Gleda gore</t>
+  </si>
+  <si>
+    <t>Gleda naprijed</t>
+  </si>
+  <si>
+    <t>Nema nagiba glave</t>
+  </si>
+  <si>
+    <t>Gleda ulijevo</t>
+  </si>
+  <si>
+    <t>Gleda udesno</t>
+  </si>
+  <si>
+    <t>Nagib glave desno</t>
+  </si>
+  <si>
+    <t>Klasifikacija pogleda (sva tri kuta)</t>
+  </si>
+  <si>
+    <t>Pitch MediaPipe (Â°)</t>
+  </si>
+  <si>
+    <t>Pitch BIWI (Â°)</t>
+  </si>
+  <si>
+    <t>Pitch Razlika (Â°)</t>
+  </si>
+  <si>
+    <t>Yaw MediaPipe (Â°)</t>
+  </si>
+  <si>
+    <t>Yaw BIWI (Â°)</t>
+  </si>
+  <si>
+    <t>Yaw Razlika (Â°)</t>
+  </si>
+  <si>
+    <t>Roll MediaPipe (Â°)</t>
+  </si>
+  <si>
+    <t>Roll BIWI (Â°)</t>
+  </si>
+  <si>
+    <t>Roll Razlika (Â°)</t>
+  </si>
+  <si>
+    <t>MP Pitch (°)</t>
+  </si>
+  <si>
+    <t>BIWI Pitch (°)</t>
+  </si>
+  <si>
+    <t>MP Yaw (°)</t>
+  </si>
+  <si>
+    <t>BIWI Yaw (°)</t>
+  </si>
+  <si>
+    <t>MP Roll (°)</t>
+  </si>
+  <si>
+    <t>BIWI Roll (°)</t>
   </si>
 </sst>
 </file>
@@ -521,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A9F1B7-95EF-4908-A524-EC826786FE6E}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -536,6 +671,7 @@
     <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="44.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -604,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>1.41</v>
       </c>
       <c r="K4" t="str">
         <f>LEFT(A4, LEN(A4)-4)</f>
@@ -620,7 +756,7 @@
       </c>
       <c r="N4">
         <f>H4</f>
-        <v>5</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -688,7 +824,7 @@
         <v>-6</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>7.81</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="0"/>
@@ -704,7 +840,7 @@
       </c>
       <c r="N6">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -730,7 +866,7 @@
         <v>13</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
@@ -746,7 +882,7 @@
       </c>
       <c r="N7">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -772,7 +908,7 @@
         <v>-7</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>7.07</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
@@ -788,7 +924,7 @@
       </c>
       <c r="N8">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -801,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>47.39</v>
+        <v>145.74</v>
       </c>
       <c r="C11">
         <v>171.14</v>
@@ -821,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>46.42</v>
+        <v>113.63</v>
       </c>
       <c r="C12">
         <v>172.75</v>
@@ -832,7 +968,7 @@
       </c>
       <c r="L12">
         <f>B11</f>
-        <v>47.39</v>
+        <v>145.74</v>
       </c>
       <c r="M12">
         <f>C11</f>
@@ -844,7 +980,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>41.47</v>
+        <v>90.3</v>
       </c>
       <c r="C13">
         <v>179.18</v>
@@ -855,7 +991,7 @@
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L16" si="5">B12</f>
-        <v>46.42</v>
+        <v>113.63</v>
       </c>
       <c r="M13">
         <f t="shared" ref="M13:M16" si="6">C12</f>
@@ -867,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>34.21</v>
+        <v>103.93</v>
       </c>
       <c r="C14">
         <v>175.42</v>
@@ -878,7 +1014,7 @@
       </c>
       <c r="L14">
         <f t="shared" si="5"/>
-        <v>41.47</v>
+        <v>90.3</v>
       </c>
       <c r="M14">
         <f t="shared" si="6"/>
@@ -890,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>38.54</v>
+        <v>113.33</v>
       </c>
       <c r="C15">
         <v>176.23</v>
@@ -901,7 +1037,7 @@
       </c>
       <c r="L15">
         <f t="shared" si="5"/>
-        <v>34.21</v>
+        <v>103.93</v>
       </c>
       <c r="M15">
         <f t="shared" si="6"/>
@@ -915,27 +1051,635 @@
       </c>
       <c r="L16">
         <f t="shared" si="5"/>
-        <v>38.54</v>
+        <v>113.33</v>
       </c>
       <c r="M16">
         <f t="shared" si="6"/>
         <v>176.23</v>
       </c>
     </row>
-    <row r="30" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>-1.81</v>
+      </c>
+      <c r="K18" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="K19" t="str">
+        <f>LEFT(A18, LEN(A18)-4)</f>
+        <v>000001</v>
+      </c>
+      <c r="L19">
+        <f>B18</f>
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>-3.53</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" ref="K20:K23" si="7">LEFT(A19, LEN(A19)-4)</f>
+        <v>000005</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ref="L20:L23" si="8">B19</f>
+        <v>-1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>-1.61</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="7"/>
+        <v>000010</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="8"/>
+        <v>-3.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>-1.31</v>
+      </c>
+      <c r="K22" t="str">
+        <f t="shared" si="7"/>
+        <v>000015</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="8"/>
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K23" t="str">
+        <f t="shared" si="7"/>
+        <v>000020</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="8"/>
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>50</v>
+      </c>
+      <c r="B29">
+        <v>-20.58</v>
+      </c>
+      <c r="C29">
+        <v>9.65</v>
+      </c>
+      <c r="D29">
+        <v>-3.69</v>
+      </c>
+      <c r="K29">
+        <f>A29</f>
+        <v>50</v>
+      </c>
+      <c r="L29">
+        <f t="shared" ref="L29:N29" si="9">B29</f>
+        <v>-20.58</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="9"/>
+        <v>9.65</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="9"/>
+        <v>-3.69</v>
+      </c>
+      <c r="O29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>350</v>
+      </c>
+      <c r="B30">
+        <v>-25.83</v>
+      </c>
+      <c r="C30">
+        <v>-24.87</v>
+      </c>
+      <c r="D30">
+        <v>6.43</v>
+      </c>
+      <c r="K30">
+        <f t="shared" ref="K30:K31" si="10">A30</f>
+        <v>350</v>
+      </c>
+      <c r="L30">
+        <f t="shared" ref="L30:L31" si="11">B30</f>
+        <v>-25.83</v>
+      </c>
+      <c r="M30">
+        <f t="shared" ref="M30:M31" si="12">C30</f>
+        <v>-24.87</v>
+      </c>
+      <c r="N30">
+        <f t="shared" ref="N30:N31" si="13">D30</f>
+        <v>6.43</v>
+      </c>
+      <c r="O30" t="s">
+        <v>25</v>
+      </c>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>508</v>
+      </c>
+      <c r="B31">
+        <v>-19.440000000000001</v>
+      </c>
+      <c r="C31">
+        <v>12.91</v>
+      </c>
+      <c r="D31">
+        <v>-13.62</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="10"/>
+        <v>508</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="11"/>
+        <v>-19.440000000000001</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="12"/>
+        <v>12.91</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="13"/>
+        <v>-13.62</v>
+      </c>
+      <c r="O31" t="s">
+        <v>24</v>
+      </c>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="P32" s="1"/>
     </row>
-    <row r="33" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P33" s="1"/>
     </row>
-    <row r="34" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" t="s">
+        <v>28</v>
+      </c>
+      <c r="O35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>50</v>
+      </c>
+      <c r="B36">
+        <v>-20.58</v>
+      </c>
+      <c r="C36">
+        <v>9.65</v>
+      </c>
+      <c r="D36">
+        <v>-3.69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36">
+        <f>A36</f>
+        <v>50</v>
+      </c>
+      <c r="L36">
+        <f t="shared" ref="L36:N36" si="14">B36</f>
+        <v>-20.58</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="14"/>
+        <v>9.65</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="14"/>
+        <v>-3.69</v>
+      </c>
+      <c r="O36" t="str">
+        <f>E36&amp;", "&amp;G36&amp;", "&amp;F36</f>
+        <v>Gleda gore, Nema nagiba glave, Gleda naprijed</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>350</v>
+      </c>
+      <c r="B37">
+        <v>-25.83</v>
+      </c>
+      <c r="C37">
+        <v>-24.87</v>
+      </c>
+      <c r="D37">
+        <v>6.43</v>
+      </c>
+      <c r="E37" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37">
+        <f t="shared" ref="K37:K38" si="15">A37</f>
+        <v>350</v>
+      </c>
+      <c r="L37">
+        <f t="shared" ref="L37:L38" si="16">B37</f>
+        <v>-25.83</v>
+      </c>
+      <c r="M37">
+        <f t="shared" ref="M37:M38" si="17">C37</f>
+        <v>-24.87</v>
+      </c>
+      <c r="N37">
+        <f t="shared" ref="N37:N38" si="18">D37</f>
+        <v>6.43</v>
+      </c>
+      <c r="O37" t="str">
+        <f t="shared" ref="O37:O38" si="19">E37&amp;", "&amp;G37&amp;", "&amp;F37</f>
+        <v>Gleda gore, Nema nagiba glave, Gleda ulijevo</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>508</v>
+      </c>
+      <c r="B38">
+        <v>-19.440000000000001</v>
+      </c>
+      <c r="C38">
+        <v>12.91</v>
+      </c>
+      <c r="D38">
+        <v>-13.62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G38" t="s">
+        <v>41</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="15"/>
+        <v>508</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="16"/>
+        <v>-19.440000000000001</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="17"/>
+        <v>12.91</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="18"/>
+        <v>-13.62</v>
+      </c>
+      <c r="O38" t="str">
+        <f t="shared" si="19"/>
+        <v>Gleda gore, Nagib glave desno, Gleda udesno</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" t="s">
+        <v>50</v>
+      </c>
+      <c r="J42" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" t="s">
+        <v>22</v>
+      </c>
+      <c r="N42" t="s">
+        <v>52</v>
+      </c>
+      <c r="O42" t="s">
+        <v>53</v>
+      </c>
+      <c r="P42" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>55</v>
+      </c>
+      <c r="R42" t="s">
+        <v>56</v>
+      </c>
+      <c r="S42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>50</v>
+      </c>
+      <c r="B43">
+        <v>-5.35</v>
+      </c>
+      <c r="C43">
+        <v>-20.58</v>
+      </c>
+      <c r="D43">
+        <v>15.23</v>
+      </c>
+      <c r="E43">
+        <v>14.09</v>
+      </c>
+      <c r="F43">
+        <v>9.65</v>
+      </c>
+      <c r="G43">
+        <v>4.45</v>
+      </c>
+      <c r="H43">
+        <v>-5.17</v>
+      </c>
+      <c r="I43">
+        <v>-3.69</v>
+      </c>
+      <c r="J43">
+        <v>1.48</v>
+      </c>
+      <c r="M43">
+        <f>A43</f>
+        <v>50</v>
+      </c>
+      <c r="N43">
+        <f t="shared" ref="N43:S43" si="20">B43</f>
+        <v>-5.35</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="20"/>
+        <v>-20.58</v>
+      </c>
+      <c r="P43">
+        <f t="shared" si="20"/>
+        <v>15.23</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="20"/>
+        <v>14.09</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="20"/>
+        <v>9.65</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="20"/>
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>350</v>
+      </c>
+      <c r="B44">
+        <v>-8.58</v>
+      </c>
+      <c r="C44">
+        <v>-25.83</v>
+      </c>
+      <c r="D44">
+        <v>17.25</v>
+      </c>
+      <c r="E44">
+        <v>-52.19</v>
+      </c>
+      <c r="F44">
+        <v>-24.87</v>
+      </c>
+      <c r="G44">
+        <v>27.33</v>
+      </c>
+      <c r="H44">
+        <v>-1.44</v>
+      </c>
+      <c r="I44">
+        <v>6.43</v>
+      </c>
+      <c r="J44">
+        <v>7.87</v>
+      </c>
+      <c r="M44">
+        <f t="shared" ref="M44:M45" si="21">A44</f>
+        <v>350</v>
+      </c>
+      <c r="N44">
+        <f t="shared" ref="N44:N45" si="22">B44</f>
+        <v>-8.58</v>
+      </c>
+      <c r="O44">
+        <f t="shared" ref="O44:O45" si="23">C44</f>
+        <v>-25.83</v>
+      </c>
+      <c r="P44">
+        <f t="shared" ref="P44:P45" si="24">D44</f>
+        <v>17.25</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" ref="Q44:Q45" si="25">E44</f>
+        <v>-52.19</v>
+      </c>
+      <c r="R44">
+        <f t="shared" ref="R44:R45" si="26">F44</f>
+        <v>-24.87</v>
+      </c>
+      <c r="S44">
+        <f t="shared" ref="S44:S45" si="27">G44</f>
+        <v>27.33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>508</v>
+      </c>
+      <c r="B45">
+        <v>-2.66</v>
+      </c>
+      <c r="C45">
+        <v>-19.440000000000001</v>
+      </c>
+      <c r="D45">
+        <v>16.78</v>
+      </c>
+      <c r="E45">
+        <v>18.87</v>
+      </c>
+      <c r="F45">
+        <v>12.91</v>
+      </c>
+      <c r="G45">
+        <v>5.96</v>
+      </c>
+      <c r="H45">
+        <v>-10.75</v>
+      </c>
+      <c r="I45">
+        <v>-13.62</v>
+      </c>
+      <c r="J45">
+        <v>2.87</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="21"/>
+        <v>508</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="22"/>
+        <v>-2.66</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="23"/>
+        <v>-19.440000000000001</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="24"/>
+        <v>16.78</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="25"/>
+        <v>18.87</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="26"/>
+        <v>12.91</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="27"/>
+        <v>5.96</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
